--- a/06-人事行政/人事刘萍萍/在招岗位详情表-第三季度(2026805加28天版）.xlsx
+++ b/06-人事行政/人事刘萍萍/在招岗位详情表-第三季度(2026805加28天版）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="14080" tabRatio="820" activeTab="2"/>
+    <workbookView windowWidth="27950" windowHeight="14080" tabRatio="820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="表一组织结构图" sheetId="12" r:id="rId1"/>
